--- a/diseases/d047/2010-2014.xlsx
+++ b/diseases/d047/2010-2014.xlsx
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32438,7 +32438,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34019,7 +34019,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36404,7 +36404,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40370,7 +40370,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42353,7 +42353,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42755,7 +42755,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43559,7 +43559,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46721,7 +46721,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47525,7 +47525,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48704,7 +48704,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49910,7 +49910,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51089,7 +51089,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -51491,7 +51491,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51893,7 +51893,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -53876,7 +53876,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55055,7 +55055,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -55457,7 +55457,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55859,7 +55859,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -57038,7 +57038,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57440,7 +57440,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -57842,7 +57842,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58244,7 +58244,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58646,7 +58646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59423,7 +59423,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59825,7 +59825,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60227,7 +60227,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60629,7 +60629,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61406,7 +61406,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61808,7 +61808,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62210,7 +62210,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -62612,7 +62612,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -63014,7 +63014,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -63791,7 +63791,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -64193,7 +64193,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -64997,7 +64997,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65774,7 +65774,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -66176,7 +66176,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -66578,7 +66578,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -66980,7 +66980,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -67757,7 +67757,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -68159,7 +68159,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68561,7 +68561,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -68963,7 +68963,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -69365,7 +69365,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -70142,7 +70142,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -70544,7 +70544,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -70946,7 +70946,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -71348,7 +71348,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">

--- a/diseases/d047/2010-2014.xlsx
+++ b/diseases/d047/2010-2014.xlsx
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32438,7 +32438,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34019,7 +34019,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36404,7 +36404,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40370,7 +40370,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42353,7 +42353,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42755,7 +42755,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43559,7 +43559,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46721,7 +46721,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47525,7 +47525,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48704,7 +48704,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49910,7 +49910,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51089,7 +51089,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -51491,7 +51491,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51893,7 +51893,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -53876,7 +53876,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55055,7 +55055,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -55457,7 +55457,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55859,7 +55859,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -57038,7 +57038,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57440,7 +57440,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -57842,7 +57842,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58244,7 +58244,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58646,7 +58646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59423,7 +59423,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59825,7 +59825,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60227,7 +60227,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60629,7 +60629,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61406,7 +61406,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61808,7 +61808,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62210,7 +62210,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -62612,7 +62612,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -63014,7 +63014,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -63791,7 +63791,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -64193,7 +64193,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -64997,7 +64997,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65774,7 +65774,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -66176,7 +66176,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -66578,7 +66578,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -66980,7 +66980,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -67757,7 +67757,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -68159,7 +68159,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68561,7 +68561,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -68963,7 +68963,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -69365,7 +69365,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -70142,7 +70142,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -70544,7 +70544,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -70946,7 +70946,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -71348,7 +71348,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">

--- a/diseases/d047/2010-2014.xlsx
+++ b/diseases/d047/2010-2014.xlsx
@@ -13395,7 +13395,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18165,7 +18165,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27678,7 +27678,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29661,7 +29661,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -30867,7 +30867,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31644,7 +31644,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32046,7 +32046,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32448,7 +32448,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33252,7 +33252,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34029,7 +34029,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34833,7 +34833,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35235,7 +35235,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36012,7 +36012,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36414,7 +36414,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36816,7 +36816,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37995,7 +37995,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38799,7 +38799,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39201,7 +39201,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39603,7 +39603,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40380,7 +40380,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -40782,7 +40782,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41184,7 +41184,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41586,7 +41586,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42363,7 +42363,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -42765,7 +42765,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43167,7 +43167,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45150,7 +45150,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45552,7 +45552,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45954,7 +45954,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46731,7 +46731,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47133,7 +47133,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47535,7 +47535,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48714,7 +48714,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49116,7 +49116,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49518,7 +49518,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -49920,7 +49920,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -50697,7 +50697,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51099,7 +51099,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51903,7 +51903,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52305,7 +52305,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53082,7 +53082,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -53484,7 +53484,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -53886,7 +53886,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54288,7 +54288,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -55065,7 +55065,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55467,7 +55467,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -56271,7 +56271,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -57048,7 +57048,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -57450,7 +57450,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -57852,7 +57852,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58254,7 +58254,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -58656,7 +58656,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59433,7 +59433,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -59835,7 +59835,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60237,7 +60237,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -60639,7 +60639,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61416,7 +61416,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -61818,7 +61818,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -62220,7 +62220,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -62622,7 +62622,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -63024,7 +63024,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -63801,7 +63801,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -64203,7 +64203,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN325" t="b">
@@ -64605,7 +64605,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65007,7 +65007,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -65784,7 +65784,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -66186,7 +66186,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -66588,7 +66588,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -66990,7 +66990,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -67767,7 +67767,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -68169,7 +68169,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -68571,7 +68571,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -68973,7 +68973,7 @@
       </c>
       <c r="AM349" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN349" t="b">
@@ -69375,7 +69375,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -70152,7 +70152,7 @@
       </c>
       <c r="AM355" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN355" t="b">
@@ -70554,7 +70554,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN357" t="b">
@@ -70956,7 +70956,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -71358,7 +71358,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN361" t="b">

--- a/diseases/d047/2010-2014.xlsx
+++ b/diseases/d047/2010-2014.xlsx
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32438,7 +32438,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34019,7 +34019,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36404,7 +36404,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40370,7 +40370,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42353,7 +42353,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42755,7 +42755,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43559,7 +43559,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46721,7 +46721,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47525,7 +47525,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48704,7 +48704,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49910,7 +49910,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51089,7 +51089,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -51491,7 +51491,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51893,7 +51893,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -53876,7 +53876,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55055,7 +55055,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -55457,7 +55457,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55859,7 +55859,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -57038,7 +57038,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57440,7 +57440,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -57842,7 +57842,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58244,7 +58244,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58646,7 +58646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59423,7 +59423,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59825,7 +59825,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60227,7 +60227,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60629,7 +60629,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61406,7 +61406,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61808,7 +61808,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62210,7 +62210,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -62612,7 +62612,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -63014,7 +63014,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -63791,7 +63791,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -64193,7 +64193,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -64997,7 +64997,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65774,7 +65774,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -66176,7 +66176,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -66578,7 +66578,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -66980,7 +66980,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -67757,7 +67757,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -68159,7 +68159,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68561,7 +68561,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -68963,7 +68963,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -69365,7 +69365,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -70142,7 +70142,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -70544,7 +70544,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -70946,7 +70946,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -71348,7 +71348,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">

--- a/diseases/d047/2010-2014.xlsx
+++ b/diseases/d047/2010-2014.xlsx
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32438,7 +32438,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34019,7 +34019,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36404,7 +36404,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40370,7 +40370,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42353,7 +42353,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42755,7 +42755,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43559,7 +43559,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46721,7 +46721,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47525,7 +47525,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48704,7 +48704,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49910,7 +49910,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51089,7 +51089,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -51491,7 +51491,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51893,7 +51893,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -53876,7 +53876,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55055,7 +55055,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -55457,7 +55457,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55859,7 +55859,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -57038,7 +57038,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57440,7 +57440,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -57842,7 +57842,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58244,7 +58244,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58646,7 +58646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59423,7 +59423,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59825,7 +59825,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60227,7 +60227,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60629,7 +60629,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61406,7 +61406,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61808,7 +61808,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62210,7 +62210,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -62612,7 +62612,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -63014,7 +63014,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -63791,7 +63791,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -64193,7 +64193,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -64997,7 +64997,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65774,7 +65774,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -66176,7 +66176,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -66578,7 +66578,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -66980,7 +66980,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -67757,7 +67757,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -68159,7 +68159,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68561,7 +68561,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -68963,7 +68963,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -69365,7 +69365,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -70142,7 +70142,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -70544,7 +70544,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -70946,7 +70946,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -71348,7 +71348,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">

--- a/diseases/d047/2010-2014.xlsx
+++ b/diseases/d047/2010-2014.xlsx
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32438,7 +32438,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34019,7 +34019,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36404,7 +36404,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40370,7 +40370,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42353,7 +42353,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42755,7 +42755,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43559,7 +43559,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46721,7 +46721,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47525,7 +47525,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48704,7 +48704,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49910,7 +49910,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51089,7 +51089,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -51491,7 +51491,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51893,7 +51893,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -53876,7 +53876,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55055,7 +55055,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -55457,7 +55457,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55859,7 +55859,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -57038,7 +57038,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57440,7 +57440,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -57842,7 +57842,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58244,7 +58244,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58646,7 +58646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59423,7 +59423,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59825,7 +59825,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60227,7 +60227,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60629,7 +60629,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61406,7 +61406,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61808,7 +61808,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62210,7 +62210,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -62612,7 +62612,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -63014,7 +63014,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -63791,7 +63791,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -64193,7 +64193,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -64997,7 +64997,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65774,7 +65774,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -66176,7 +66176,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -66578,7 +66578,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -66980,7 +66980,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -67757,7 +67757,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -68159,7 +68159,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68561,7 +68561,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -68963,7 +68963,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -69365,7 +69365,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -70142,7 +70142,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -70544,7 +70544,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -70946,7 +70946,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -71348,7 +71348,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
